--- a/vehicle_inspection_forms/044_vehicle_take_over_report_form_template--vehicle_inspection_forms.xlsx
+++ b/vehicle_inspection_forms/044_vehicle_take_over_report_form_template--vehicle_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1122,8 +1122,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'adequate'}</t>
+          <t>adequate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Adequate'}</t>
+          <t>Adequate</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'empty'}</t>
+          <t>empty</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Empty'}</t>
+          <t>Empty</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'not_checked'}</t>
+          <t>not_checked</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Not Checked'}</t>
+          <t>Not Checked</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'clean'}</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Clean'}</t>
+          <t>Clean</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'dirty'}</t>
+          <t>dirty</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Dirty'}</t>
+          <t>Dirty</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'employee_a'}</t>
+          <t>employee_a</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Employee A'}</t>
+          <t>Employee A</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'employee_b'}</t>
+          <t>employee_b</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Employee B'}</t>
+          <t>Employee B</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'employee_c'}</t>
+          <t>employee_c</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Employee C'}</t>
+          <t>Employee C</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
